--- a/artfynd/A 31116-2023 artfynd.xlsx
+++ b/artfynd/A 31116-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137452762</v>
       </c>
       <c r="B2" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137452759</v>
       </c>
       <c r="B3" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>137452764</v>
       </c>
       <c r="B4" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1020,7 +1020,7 @@
         <v>137452754</v>
       </c>
       <c r="B5" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>137452758</v>
       </c>
       <c r="B6" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1239,7 +1239,7 @@
         <v>137452757</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>137452763</v>
       </c>
       <c r="B8" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>137452756</v>
       </c>
       <c r="B9" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1575,7 +1575,7 @@
         <v>137452760</v>
       </c>
       <c r="B10" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         <v>137452761</v>
       </c>
       <c r="B11" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1799,7 +1799,7 @@
         <v>137452765</v>
       </c>
       <c r="B12" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
